--- a/output/laminas_comunales/comunal_o_ocup_a_2018_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2018_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,202 @@
         </is>
       </c>
       <c r="C2">
+        <v>52.527645111084</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>52.4538078308105</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>47.1512107849121</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>47.0127601623535</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>41.8319664001465</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>41.6937675476074</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C8">
         <v>35.6606597900391</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>35.5510406494141</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>29.7353229522705</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>29.6493949890137</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>29.3115634918213</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>29.2809562683105</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>9.38278770446777</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>9.314496994018549</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_o_ocup_a_2018_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2018_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,202 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>52.527645111084</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>52.4538078308105</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>47.1512107849121</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>47.0127601623535</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>41.8319664001465</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>41.6937675476074</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C8">
         <v>35.6606597900391</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>35.5510406494141</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>29.7353229522705</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>29.6493949890137</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>29.3115634918213</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>29.2809562683105</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>9.38278770446777</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>15101</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>9.314496994018549</v>
       </c>
     </row>
   </sheetData>
